--- a/src/test/resources/fixtures/extraccion.xlsx
+++ b/src/test/resources/fixtures/extraccion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1554,83 +1554,296 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="n">
+        <v>55751</v>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Regresion num-num</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tresp1@x</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Obj</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>CTR-100</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>99642</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101770</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Regresion num dobles</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tresp2@x</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Obj</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>CTR-200</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>90014</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>20</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>138074</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Regresion num filtrada Sup</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tresp1@x</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Obj</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>CTR-100</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>99641</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/test/resources/fixtures/extraccion.xlsx
+++ b/src/test/resources/fixtures/extraccion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1767,83 +1767,158 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P-015</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Regresion responsable MAYUS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRESP1@x</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Obj V</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>CTR-100</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>M-1009</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/test/resources/fixtures/extraccion.xlsx
+++ b/src/test/resources/fixtures/extraccion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1842,83 +1842,158 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P-016</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Regresion responsable con padding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MG002   </t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Obj W</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>CTR-100</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>M-1010</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/test/resources/fixtures/extraccion.xlsx
+++ b/src/test/resources/fixtures/extraccion.xlsx
@@ -413,1368 +413,1387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Peticion</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Aplicaci_Activi</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Usuario_Resp_Tecnico</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Horas_AutoriTotPeticion</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Horas_RealizadoTot</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Estado_Distribucion</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Planificacion</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Objeto_EstudioPeticion</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Codigo_Facturacion</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Recurso</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Funcion</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>UltimaPrevision_Horas_Mes</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Realizadas_Horas_Mes</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Total_Horas_Autorizadas_Recurso</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Total_Horas_Realizadas_Recurso</t>
+          <t>EXPORT JIRA - Closure Report</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P-001</t>
+          <t>Project Key</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Migracion BBDD</t>
+          <t>Issue Key</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>Aplicación BFA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Labels</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G2" t="n">
-        <v>12</v>
+          <t>Parent Issue Summary</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Issue Type</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>Time entry: User</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Obj A</t>
+          <t>Time entry: Date</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CTR-100</t>
+          <t>Component Name</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>M-1001</t>
+          <t>Time entry: Description</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>20</v>
+          <t>Matricula</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Funcion</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P-002</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Refactor UI</t>
+          <t>PROJ-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>back</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
+          <t>epic-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sum1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>u1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Obj B</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CTR-100</t>
+          <t>P-001</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>M-1002</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>M-1001</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>20</v>
-      </c>
-      <c r="O3" t="n">
-        <v>15</v>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P-003</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>API v2</t>
+          <t>PROJ-2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cerrada</t>
+          <t>back</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tresp2@x</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25</v>
+          <t>epic-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sum2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>u1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Obj C</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CTR-200</t>
+          <t>P-001</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>M-1003</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>M-1001</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P-004</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dashboards</t>
+          <t>PROJ-3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>back</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tresp2@x</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
+          <t>epic-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sum3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>u1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Obj D</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CTR-200</t>
+          <t>P-001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>M-1004</t>
+          <t>t3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>30</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10</v>
+          <t>M-1001</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P-005</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Integracion SSO</t>
+          <t>PROJ-4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JX</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
+          <t>epic-2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sum4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>u2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Obj E</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CTR-100</t>
+          <t>P-002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>M-1001</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>M-1002</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P6" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P-006</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alertas</t>
+          <t>PROJ-5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tresp3@x</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8</v>
+          <t>epic-3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>sum5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>u3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Obj F</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CTR-300</t>
+          <t>P-003</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>M-1005</t>
+          <t>t5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>M-1003</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>acc2</t>
+        </is>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q7" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P-007</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Migracion cloud</t>
+          <t>PROJ-6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="n">
-        <v>40</v>
+          <t>epic-3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>sum6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>u3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Obj G</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>CTR-100</t>
+          <t>P-003</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>M-1001</t>
+          <t>t6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>M-1003</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>50</v>
-      </c>
-      <c r="O8" t="n">
-        <v>15</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>acc2</t>
+        </is>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P-008</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>PROJ-7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cerrada</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tresp2@x</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
+          <t>epic-4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>sum7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>u4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Obj H</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CTR-200</t>
+          <t>P-004</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>M-1002</t>
+          <t>t7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>M-1004</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>acc2</t>
+        </is>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P-009</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Perf mejora</t>
+          <t>PROJ-8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>JX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>sso</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tresp2@x</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>35</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20</v>
+          <t>epic-5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sum8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>u1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Obj I</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CTR-200</t>
+          <t>P-005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>M-1003</t>
+          <t>t8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>M-1001</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P-010</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>PROJ-9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>HW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>alrt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tresp3@x</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
+          <t>epic-6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>sum9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>u5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Obj J</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CTR-300</t>
+          <t>P-006</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>M-1006</t>
+          <t>t9</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>M-1005</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>acc3</t>
+        </is>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P-011</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZZ-App nueva (sin mapeo)</t>
+          <t>PROJ-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>back</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tresp3@x</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>18</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
+          <t>epic-7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>sum10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>u1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Obj K</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CTR-300</t>
+          <t>P-007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>M-1007</t>
+          <t>t10</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>M-1001</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P-012</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Refactor tests</t>
+          <t>PROJ-11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10</v>
+          <t>epic-8</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>sum11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>u2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Obj L</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CTR-100</t>
+          <t>P-008</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>t11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>M-1002</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P-013</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Import CSV</t>
+          <t>PROJ-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tresp2@x</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
+          <t>epic-9</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sum12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>u3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Obj M</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>CTR-200</t>
+          <t>P-009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>M-1008</t>
+          <t>t12</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>M-1003</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>acc2</t>
+        </is>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PROJ-13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>epic-10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>sum13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>u6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P-010</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>t13</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>M-1006</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>acc3</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PROJ-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>epic-12</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>sum14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>u2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>P-012</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>t14</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>M-1002</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>acc1</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PROJ-15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>imp</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>epic-13</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>sum15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>u7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>P-013</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>t15</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>M-1008</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>acc2</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PROJ-16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>epic-14</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>sum16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>u6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>P-014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Export Parquet</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>KE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Abierta</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>tresp3@x</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>28</v>
-      </c>
-      <c r="G15" t="n">
-        <v>12</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Obj N</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>CTR-300</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>t16</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>M-1006</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>7</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>55751</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Regresion num-num</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Abierta</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>50</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Obj</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>CTR-100</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>99642</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>101770</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Regresion num dobles</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Abierta</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>tresp2@x</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Obj</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>CTR-200</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>90014</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>20</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>138074</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Regresion num filtrada Sup</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>HE</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Abierta</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>tresp1@x</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>30</v>
-      </c>
-      <c r="G18" t="n">
-        <v>9</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Obj</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>CTR-100</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>99641</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>15</v>
-      </c>
-      <c r="O18" t="n">
-        <v>9</v>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>acc3</t>
+        </is>
       </c>
       <c r="P18" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q18" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P-015</t>
+          <t>PROJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Regresion responsable MAYUS</t>
+          <t>PROJ-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1784,219 +1803,786 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>reg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TRESP1@x</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
+          <t>epic-r1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>sumR1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>u1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Obj V</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CTR-100</t>
+          <t>55751</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>M-1009</t>
+          <t>tR1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>99642</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>accR</t>
+        </is>
       </c>
       <c r="P19" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PROJ-21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>reg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>epic-r2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>sumR2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>u2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>101770</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>tR2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>90014</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>accR</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PROJ-22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>reg</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>epic-r2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>sumR3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>u2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>101770</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>tR3</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>90014</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>accR</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PROJ-23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>reg</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>epic-r3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>sumR4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>u3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>138074</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>tR4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>99641</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>accR</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PROJ-24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>reg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>epic-r3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>sumR5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>u3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>138074</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>tR5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>99641</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>accR</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PROJ-25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pad</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>epic-pad</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>sumR6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>u8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>P-016</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Regresion responsable con padding</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>tR6</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>M-1010</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>accR</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PROJ-30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>huerf</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>epic-h1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>sumH1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>u4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>TICKETS</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>tH1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>accH</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PROJ-31</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>huerf</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>epic-h1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>sumH2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>u4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TICKETS</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>tH2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>accH</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PROJ-32</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>huerf</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>epic-h2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>sumH3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>u5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>tH3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>90014</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>accH</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PROJ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PROJ-33</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Abierta</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MG002   </t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>20</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Obj W</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>CTR-100</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>M-1010</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>huerf</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>epic-h3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>sumH4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>u1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>tH4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>MAT-HUERFANO</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Dev</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>accH</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
